--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
   </si>
 </sst>
 </file>
@@ -926,7 +935,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -956,6 +965,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920092</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,10 +85,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>IVAN</t>
   </si>
   <si>
     <t>ELEAZAR RIGOBERTO</t>
@@ -544,16 +562,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -707,7 +728,7 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -864,16 +885,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -935,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -967,24 +991,70 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920092</v>
+        <v>20330051920069</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920102</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920092</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="G2">
+      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -88,25 +88,16 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>IVAN</t>
   </si>
   <si>
     <t>ELEAZAR RIGOBERTO</t>
@@ -536,16 +527,16 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H3">
         <v>7.9</v>
@@ -705,7 +696,7 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -859,16 +850,16 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H3">
         <v>7.9</v>
@@ -959,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -997,10 +988,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1014,47 +1005,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920102</v>
+        <v>19330051920092</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920092</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,19 +88,10 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
   </si>
 </sst>
 </file>
@@ -693,16 +684,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>63.64</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -739,16 +733,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -853,13 +850,13 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>87.88</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H3">
         <v>7.9</v>
@@ -914,7 +911,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -950,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,10 +985,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1000,29 +997,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920092</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
   </si>
 </sst>
 </file>
@@ -492,19 +483,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -596,19 +587,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -661,16 +652,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>69.44</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,16 +704,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>38.71</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -759,16 +756,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>38.71</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -821,19 +821,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -885,7 +885,7 @@
         <v>64.52</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -925,19 +925,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -977,29 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920069</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -678,19 +678,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>66.67</v>
+      </c>
+      <c r="H3">
         <v>8</v>
-      </c>
-      <c r="F3">
-        <v>21</v>
-      </c>
-      <c r="G3">
-        <v>63.64</v>
-      </c>
-      <c r="H3">
-        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -704,16 +704,16 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>38.71</v>
+        <v>41.94</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -756,16 +756,16 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>38.71</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -937,7 +937,7 @@
         <v>90.31999999999999</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,60 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
 </sst>
 </file>
@@ -483,19 +537,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -509,19 +563,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -561,19 +615,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -587,19 +641,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>87.09999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -652,19 +706,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>69.44</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -678,19 +732,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -730,19 +784,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -756,19 +810,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>87.09999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -821,19 +875,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -847,19 +901,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -899,10 +953,10 @@
         <v>38</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>6</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>32</v>
@@ -911,7 +965,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -925,19 +979,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -977,6 +1031,144 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920019</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920075</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920077</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920070</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920098</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920059</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -88,52 +88,58 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>JOAQUIN</t>
   </si>
   <si>
     <t>ABRIL</t>
   </si>
   <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
     <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>JUAN ANTONIO</t>
   </si>
   <si>
     <t>DANIEL</t>
@@ -1001,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,10 +1045,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1056,16 +1062,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1079,16 +1085,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920077</v>
+        <v>20330051920070</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1102,22 +1108,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920070</v>
+        <v>19330051920014</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1131,10 +1137,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1148,7 +1154,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920059</v>
+        <v>20330051920075</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1157,7 +1163,7 @@
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1166,6 +1172,29 @@
         <v>13</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920059</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -88,61 +88,58 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ESPINOZA</t>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
     <t>ABRIL</t>
   </si>
   <si>
-    <t>ADRIAN</t>
+    <t>MARCO ANTONIO</t>
   </si>
   <si>
     <t>OSVALDO</t>
   </si>
   <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
   </si>
 </sst>
 </file>
@@ -543,10 +540,10 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -595,19 +592,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>64.52</v>
+        <v>77.42</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -712,10 +709,10 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -738,19 +735,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>78.79000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -764,19 +761,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>41.94</v>
+        <v>77.42</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -881,10 +878,10 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -910,16 +907,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>90.91</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -933,19 +930,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>64.52</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1048,7 +1045,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1062,16 +1059,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920077</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1091,10 +1088,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1108,16 +1105,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920014</v>
+        <v>19330051920032</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1131,22 +1128,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920098</v>
+        <v>19330051920036</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1154,7 +1151,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920075</v>
+        <v>19330051920014</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1163,13 +1160,13 @@
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1177,22 +1174,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920059</v>
+        <v>19330051920098</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>1</v>
